--- a/members_data/collaborateurs.xlsx
+++ b/members_data/collaborateurs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/frederiquebaron/Desktop/AstroQuebec_website/members_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D80EF788-C496-2F49-95E8-D6D176A9448E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35F21896-1996-6743-80D2-D34431F5617A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="940" yWindow="760" windowWidth="29300" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30240" yWindow="2760" windowWidth="27320" windowHeight="15360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="databrut" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="143">
   <si>
     <t>Nom / Last Name</t>
   </si>
@@ -77,9 +77,6 @@
     <t>Collaborateur</t>
   </si>
   <si>
-    <t>Université du Québec à Montréal [UQAM]</t>
-  </si>
-  <si>
     <t>Carignan</t>
   </si>
   <si>
@@ -104,12 +101,6 @@
     <t>Jean</t>
   </si>
   <si>
-    <t>Agence spatiale canadienne [ASC]</t>
-  </si>
-  <si>
-    <t>ABB Group</t>
-  </si>
-  <si>
     <t>Grandmont</t>
   </si>
   <si>
@@ -249,15 +240,250 @@
   </si>
   <si>
     <t>Collaboratrice</t>
+  </si>
+  <si>
+    <t>Albert</t>
+  </si>
+  <si>
+    <t>Loic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">albert@astro.umontreal.ca </t>
+  </si>
+  <si>
+    <t>Artigau</t>
+  </si>
+  <si>
+    <t>Étienne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">artigau@astro.umontreal.ca </t>
+  </si>
+  <si>
+    <t>Baron</t>
+  </si>
+  <si>
+    <t>Frédérique</t>
+  </si>
+  <si>
+    <t>frederique.baron@umontreal.ca</t>
+  </si>
+  <si>
+    <t>Beaulieu</t>
+  </si>
+  <si>
+    <t>Sylvie Florence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">beaulieu@astro.umontreal.ca </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brousseau </t>
+  </si>
+  <si>
+    <t>Denis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">denis.brousseau@copl.ulaval.ca </t>
+  </si>
+  <si>
+    <t>Cook</t>
+  </si>
+  <si>
+    <t>Neil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">neil.cook@umontreal.ca </t>
+  </si>
+  <si>
+    <t>Hoffman</t>
+  </si>
+  <si>
+    <t>Kelsey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kelsey.hoffman@ubishops.ca </t>
+  </si>
+  <si>
+    <t>Université Bishop's</t>
+  </si>
+  <si>
+    <t>Lessard-Hamel</t>
+  </si>
+  <si>
+    <t>Béatrice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">beatrice.lessard-hamel.1@ulaval.ca </t>
+  </si>
+  <si>
+    <t>Malo</t>
+  </si>
+  <si>
+    <t>Lison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">malo@astro.umontreal.ca </t>
+  </si>
+  <si>
+    <t>Naud</t>
+  </si>
+  <si>
+    <t>Marie-Eve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">naud@astro.umontreal.ca </t>
+  </si>
+  <si>
+    <t>Ouellette</t>
+  </si>
+  <si>
+    <t>Nathalie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nathalie@astro.umontreal.ca </t>
+  </si>
+  <si>
+    <t>Richer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacques </t>
+  </si>
+  <si>
+    <t xml:space="preserve">jacques.richer@umontreal.ca </t>
+  </si>
+  <si>
+    <t>Turcotte</t>
+  </si>
+  <si>
+    <t>Sylvain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sturcott@ubishops.ca </t>
+  </si>
+  <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t>Heidi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">heidi.white@umontreal.ca </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dallas </t>
+  </si>
+  <si>
+    <t>Wulf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dallas.wulf@mail.mcgill.ca </t>
+  </si>
+  <si>
+    <t>Eesha</t>
+  </si>
+  <si>
+    <t>Das Gupta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eesha.dasgupta@mcgill.ca </t>
+  </si>
+  <si>
+    <t>St-Antoine</t>
+  </si>
+  <si>
+    <t>Jonathan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jonathan.st-antoine@umontreal.ca </t>
+  </si>
+  <si>
+    <t>Turbide</t>
+  </si>
+  <si>
+    <t>Luc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">l.turbide@umontreal.ca </t>
+  </si>
+  <si>
+    <t>Robichaud</t>
+  </si>
+  <si>
+    <t>Fidèle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">robichaud@astro.umontreal.ca </t>
+  </si>
+  <si>
+    <t xml:space="preserve">O'Brien  </t>
+  </si>
+  <si>
+    <t>Stephen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stephan.obrien@mcgill.ca </t>
+  </si>
+  <si>
+    <t>Rudyk</t>
+  </si>
+  <si>
+    <t>Ted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ted.rudyk@umontreal.ca 	</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vallée </t>
+  </si>
+  <si>
+    <t>Philippe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vallee@astro.umontreal.ca </t>
+  </si>
+  <si>
+    <t>David-Uraz</t>
+  </si>
+  <si>
+    <t>Alexandre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alexandre.david-uraz@mcgill.ca 		</t>
+  </si>
+  <si>
+    <t>Brassard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brassard@astro.umontreal.ca </t>
+  </si>
+  <si>
+    <t>Université du Québec à Montréal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agence spatiale canadienne </t>
+  </si>
+  <si>
+    <t>ABB</t>
+  </si>
+  <si>
+    <t>Cosmodome</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="33" x14ac:knownFonts="1">
+  <fonts count="32" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -476,23 +702,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
@@ -794,82 +1003,81 @@
   </borders>
   <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="42"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="42"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="42" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="42" applyFill="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="42" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="42" applyFill="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="42" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="42" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="42" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="43">
@@ -1263,7 +1471,7 @@
         <v>11</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -1277,10 +1485,10 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -1288,16 +1496,16 @@
     </row>
     <row r="4" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
         <v>13</v>
       </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
       <c r="C4" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -1305,7 +1513,7 @@
     </row>
     <row r="5" spans="1:5" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
         <v>6</v>
@@ -1314,140 +1522,143 @@
         <v>11</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
         <v>17</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A7" s="22" t="s">
+      <c r="B7" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="22" t="s">
-        <v>20</v>
-      </c>
       <c r="C7" t="s">
         <v>11</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
         <v>11</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
         <v>11</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E9" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
         <v>11</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E10" t="s">
-        <v>22</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
+      </c>
+      <c r="E11" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B12" t="s">
         <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E12" t="s">
-        <v>22</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
         <v>11</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
@@ -1455,16 +1666,16 @@
     </row>
     <row r="14" spans="1:5" ht="15" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
         <v>11</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
@@ -1472,50 +1683,50 @@
     </row>
     <row r="15" spans="1:5" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E15" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E16" t="s">
-        <v>22</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C17" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E17" t="s">
         <v>7</v>
@@ -1523,121 +1734,467 @@
     </row>
     <row r="18" spans="1:5" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C18" t="s">
         <v>11</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E18" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C19" t="s">
         <v>11</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E19" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B20" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C20" t="s">
         <v>11</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E20" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A21" s="20"/>
-      <c r="B21" s="20"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="20"/>
-    </row>
-    <row r="22" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A22" s="16"/>
-      <c r="D22" s="2"/>
-    </row>
-    <row r="23" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="D23" s="2"/>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>67</v>
+      </c>
+      <c r="B21" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E21" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>70</v>
+      </c>
+      <c r="B22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A23" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="B23" t="s">
+        <v>74</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E23" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="24" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="D24" s="2"/>
-    </row>
-    <row r="25" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="D25" s="2"/>
-    </row>
-    <row r="26" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A26" s="20"/>
-      <c r="B26" s="20"/>
-      <c r="D26" s="21"/>
-      <c r="E26" s="20"/>
-    </row>
-    <row r="27" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="D27" s="2"/>
+      <c r="A24" t="s">
+        <v>76</v>
+      </c>
+      <c r="B24" t="s">
+        <v>77</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E24" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>79</v>
+      </c>
+      <c r="B25" t="s">
+        <v>80</v>
+      </c>
+      <c r="C25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E25" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E26" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A27" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="B27" t="s">
+        <v>86</v>
+      </c>
+      <c r="C27" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E27" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="28" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="D28" s="2"/>
-    </row>
-    <row r="29" spans="1:5" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A30" s="20"/>
-      <c r="B30" s="20"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="20"/>
+      <c r="A28" t="s">
+        <v>89</v>
+      </c>
+      <c r="B28" t="s">
+        <v>90</v>
+      </c>
+      <c r="C28" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E28" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>92</v>
+      </c>
+      <c r="B29" t="s">
+        <v>93</v>
+      </c>
+      <c r="C29" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E29" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>95</v>
+      </c>
+      <c r="B30" t="s">
+        <v>96</v>
+      </c>
+      <c r="C30" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E30" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="31" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="D31" s="2"/>
+      <c r="A31" t="s">
+        <v>98</v>
+      </c>
+      <c r="B31" t="s">
+        <v>99</v>
+      </c>
+      <c r="C31" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E31" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="32" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="D32" s="2"/>
-    </row>
-    <row r="33" spans="4:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="D33" s="2"/>
-    </row>
-    <row r="34" spans="4:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="D34" s="2"/>
-    </row>
-    <row r="35" spans="4:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="D35" s="2"/>
-    </row>
-    <row r="36" spans="4:4" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="37" spans="4:4" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="38" spans="4:4" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="39" spans="4:4" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="40" spans="4:4" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="41" spans="4:4" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="42" spans="4:4" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="43" spans="4:4" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="44" spans="4:4" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="45" spans="4:4" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="46" spans="4:4" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="47" spans="4:4" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="48" spans="4:4" ht="15" x14ac:dyDescent="0.2"/>
+      <c r="A32" t="s">
+        <v>101</v>
+      </c>
+      <c r="B32" t="s">
+        <v>102</v>
+      </c>
+      <c r="C32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E32" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>104</v>
+      </c>
+      <c r="B33" t="s">
+        <v>105</v>
+      </c>
+      <c r="C33" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E33" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>107</v>
+      </c>
+      <c r="B34" t="s">
+        <v>108</v>
+      </c>
+      <c r="C34" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E34" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>110</v>
+      </c>
+      <c r="B35" t="s">
+        <v>111</v>
+      </c>
+      <c r="C35" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E35" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>113</v>
+      </c>
+      <c r="B36" t="s">
+        <v>114</v>
+      </c>
+      <c r="C36" t="s">
+        <v>11</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E36" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>116</v>
+      </c>
+      <c r="B37" t="s">
+        <v>117</v>
+      </c>
+      <c r="C37" t="s">
+        <v>11</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E37" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>119</v>
+      </c>
+      <c r="B38" t="s">
+        <v>120</v>
+      </c>
+      <c r="C38" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E38" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>122</v>
+      </c>
+      <c r="B39" t="s">
+        <v>123</v>
+      </c>
+      <c r="C39" t="s">
+        <v>11</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E39" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>125</v>
+      </c>
+      <c r="B40" t="s">
+        <v>126</v>
+      </c>
+      <c r="C40" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E40" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>128</v>
+      </c>
+      <c r="B41" t="s">
+        <v>129</v>
+      </c>
+      <c r="C41" t="s">
+        <v>11</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E41" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>131</v>
+      </c>
+      <c r="B42" t="s">
+        <v>132</v>
+      </c>
+      <c r="C42" t="s">
+        <v>11</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E42" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>134</v>
+      </c>
+      <c r="B43" t="s">
+        <v>135</v>
+      </c>
+      <c r="C43" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E43" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>137</v>
+      </c>
+      <c r="B44" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E44" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="15" x14ac:dyDescent="0.2"/>
+    <row r="46" spans="1:5" ht="15" x14ac:dyDescent="0.2"/>
+    <row r="47" spans="1:5" ht="15" x14ac:dyDescent="0.2"/>
+    <row r="48" spans="1:5" ht="15" x14ac:dyDescent="0.2"/>
     <row r="49" ht="15" x14ac:dyDescent="0.2"/>
     <row r="50" ht="15" x14ac:dyDescent="0.2"/>
     <row r="51" ht="15" x14ac:dyDescent="0.2"/>
@@ -2720,8 +3277,32 @@
     <hyperlink ref="D20" r:id="rId17" display="https://listes.umontreal.ca/wws/editsubscriber/craq_collaborateurs?email=rutledge%40physics.mcgill.ca&amp;previous_action=review" xr:uid="{57354A0F-3467-1B4D-AC2A-35E06831B3F0}"/>
     <hyperlink ref="D18" r:id="rId18" display="mailto:carterrhea@astro.umontreal.ca" xr:uid="{532B4960-15EC-C142-8E52-ED1588888265}"/>
     <hyperlink ref="D17" r:id="rId19" display="https://listes.umontreal.ca/wws/editsubscriber/craq_collaborateurs?email=vincent%40astro.umontreal.ca&amp;previous_action=review" xr:uid="{8F6F0B37-E052-5844-B199-EED3CB28DAD3}"/>
+    <hyperlink ref="D35" r:id="rId20" display="https://listes.umontreal.ca/wws/editsubscriber/craq_collaborateurs?email=dallas.wulf%40mail.mcgill.ca&amp;previous_action=review" xr:uid="{E8B9944C-02B4-3848-9BF1-46CB1E3FFF15}"/>
+    <hyperlink ref="D36" r:id="rId21" display="https://listes.umontreal.ca/wws/editsubscriber/craq_collaborateurs?email=eesha.dasgupta%40mcgill.ca&amp;previous_action=review" xr:uid="{DC09343C-0E73-9A4B-9ACE-6223BC68DDD8}"/>
+    <hyperlink ref="D37" r:id="rId22" display="https://listes.umontreal.ca/wws/editsubscriber/craq_collaborateurs?email=jonathan.st-antoine%40umontreal.ca&amp;previous_action=review" xr:uid="{A299285D-A4F5-C84A-960F-1E71DADEDDC2}"/>
+    <hyperlink ref="D38" r:id="rId23" display="https://listes.umontreal.ca/wws/editsubscriber/craq_collaborateurs?email=l.turbide%40umontreal.ca&amp;previous_action=review" xr:uid="{822A474D-3907-9947-9EE5-7321ACF5DCC3}"/>
+    <hyperlink ref="D29" r:id="rId24" display="https://listes.umontreal.ca/wws/editsubscriber/craq_collaborateurs?email=malo%40astro.umontreal.ca&amp;previous_action=review" xr:uid="{78A8360F-0628-5342-ABA8-EA07856E92C4}"/>
+    <hyperlink ref="D31" r:id="rId25" display="https://listes.umontreal.ca/wws/editsubscriber/craq_collaborateurs?email=nathalie%40astro.umontreal.ca&amp;previous_action=review" xr:uid="{613FDDBE-BFA3-4B44-A3AE-BE5F2D2C27DD}"/>
+    <hyperlink ref="D30" r:id="rId26" display="https://listes.umontreal.ca/wws/editsubscriber/craq_collaborateurs?email=naud%40astro.umontreal.ca&amp;previous_action=review" xr:uid="{EEE90551-AE9B-B84F-A3D4-2513D01C21A4}"/>
+    <hyperlink ref="D26" r:id="rId27" display="https://listes.umontreal.ca/wws/editsubscriber/craq_collaborateurs?email=neil.cook%40umontreal.ca&amp;previous_action=review" xr:uid="{117639E3-798D-7C4C-936D-B93833B69D81}"/>
+    <hyperlink ref="D39" r:id="rId28" display="https://listes.umontreal.ca/wws/editsubscriber/craq_collaborateurs?email=robichaud%40astro.umontreal.ca&amp;previous_action=review" xr:uid="{C3FF7E2D-9C84-0E41-B1FA-679610E738AC}"/>
+    <hyperlink ref="D40" r:id="rId29" display="https://listes.umontreal.ca/wws/editsubscriber/craq_collaborateurs?email=stephan.obrien%40mcgill.ca&amp;previous_action=review" xr:uid="{91E8CA52-6D04-6340-9A3E-F6C6FD9F3A62}"/>
+    <hyperlink ref="D41" r:id="rId30" xr:uid="{97CE0AD0-3D67-FA49-B892-3DE4D14BDE3B}"/>
+    <hyperlink ref="D42" r:id="rId31" xr:uid="{407611C5-6426-FA40-9DD9-34692FCC8E48}"/>
+    <hyperlink ref="D21" r:id="rId32" xr:uid="{1FBA779D-FB8E-E549-B46E-2B0D4FBECFEA}"/>
+    <hyperlink ref="D43" r:id="rId33" xr:uid="{C348A4CC-B516-1143-93AE-20EDF613F024}"/>
+    <hyperlink ref="D22" r:id="rId34" xr:uid="{2D1C5113-A179-CD4C-AD93-4D142CFF4057}"/>
+    <hyperlink ref="D23" r:id="rId35" xr:uid="{2872715D-9127-0E46-BBA6-B9FFD859645A}"/>
+    <hyperlink ref="D28" r:id="rId36" xr:uid="{06DFA569-B146-2943-A7FC-632BD0B641AF}"/>
+    <hyperlink ref="D24" r:id="rId37" xr:uid="{C4442CE2-02C4-8141-9B15-01D5FAFE9EA1}"/>
+    <hyperlink ref="D44" r:id="rId38" display="https://listes.umontreal.ca/wws/editsubscriber/craq_collaborateurs?email=brassard%40astro.umontreal.ca&amp;previous_action=review" xr:uid="{93A59F58-57CF-954F-960A-7050CA065EFF}"/>
+    <hyperlink ref="D25" r:id="rId39" display="https://listes.umontreal.ca/wws/editsubscriber/craq_collaborateurs?email=denis.brousseau%40copl.ulaval.ca&amp;previous_action=review" xr:uid="{9A3E5E6F-6552-C748-967D-9F2BC6FBF8D8}"/>
+    <hyperlink ref="D34" r:id="rId40" display="https://listes.umontreal.ca/wws/editsubscriber/craq_collaborateurs?email=heidi.white%40umontreal.ca&amp;previous_action=review" xr:uid="{FE6454F3-E7B8-4244-B4A5-8E9124175DBF}"/>
+    <hyperlink ref="D32" r:id="rId41" display="https://listes.umontreal.ca/wws/editsubscriber/craq_collaborateurs?email=jacques.richer%40umontreal.ca&amp;previous_action=review" xr:uid="{499F1CA7-7A98-BB4B-853D-C69EAC790038}"/>
+    <hyperlink ref="D27" r:id="rId42" xr:uid="{FF74E593-7F54-6943-BF6F-B1EDA99100A2}"/>
+    <hyperlink ref="D33" r:id="rId43" display="https://listes.umontreal.ca/wws/editsubscriber/craq_collaborateurs?email=sturcott%40ubishops.ca&amp;previous_action=review" xr:uid="{98C5FFA2-59DB-6D46-AD59-E10D19529FA5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId20"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId44"/>
 </worksheet>
 </file>